--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -450,10 +450,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2381611466407776</v>
+        <v>0.3352309465408325</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1787420362234116</v>
+        <v>0.3035429418087006</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1670990735292435</v>
+        <v>0.294698178768158</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1998955905437469</v>
+        <v>0.3082067370414734</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +494,10 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1901446431875229</v>
+        <v>0.3024156391620636</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2176174372434616</v>
+        <v>0.3188870251178741</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1806866824626923</v>
+        <v>0.2729175388813019</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +527,10 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2380498945713043</v>
+        <v>0.3027096390724182</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.233338475227356</v>
+        <v>0.3008955419063568</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2632879316806793</v>
+        <v>0.3119738101959229</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.267630010843277</v>
+        <v>0.3028473854064941</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703481614589691</v>
+        <v>0.2963594794273376</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2591722309589386</v>
+        <v>0.2799627482891083</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +593,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2866141200065613</v>
+        <v>0.3011156320571899</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +604,10 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2840158939361572</v>
+        <v>0.3097865581512451</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.329104870557785</v>
+        <v>0.3424755930900574</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3149282336235046</v>
+        <v>0.3291063606739044</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +637,10 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2867178618907928</v>
+        <v>0.3277017176151276</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3245745003223419</v>
+        <v>0.3446286618709564</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +659,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2630676925182343</v>
+        <v>0.3140000402927399</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2354423701763153</v>
+        <v>0.3034732341766357</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2352105975151062</v>
+        <v>0.3103814721107483</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +692,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2326998710632324</v>
+        <v>0.3156424462795258</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +703,10 @@
         <v>0</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2328511476516724</v>
+        <v>0.3098143637180328</v>
       </c>
     </row>
     <row r="26">
@@ -714,10 +714,10 @@
         <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.250992476940155</v>
+        <v>0.3161989748477936</v>
       </c>
     </row>
     <row r="27">
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2467264086008072</v>
+        <v>0.3218830227851868</v>
       </c>
     </row>
     <row r="28">
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2920398712158203</v>
+        <v>0.3440283238887787</v>
       </c>
     </row>
     <row r="29">
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2850879430770874</v>
+        <v>0.3393272459506989</v>
       </c>
     </row>
     <row r="30">
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2998711168766022</v>
+        <v>0.3318997919559479</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.215909019112587</v>
+        <v>0.2955625951290131</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1847217679023743</v>
+        <v>0.2794621586799622</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2078933864831924</v>
+        <v>0.2908841073513031</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2065069973468781</v>
+        <v>0.2892663776874542</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2093569338321686</v>
+        <v>0.2934877574443817</v>
       </c>
     </row>
     <row r="36">
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2756026089191437</v>
+        <v>0.3180401623249054</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1479359865188599</v>
+        <v>0.2548227906227112</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1436859518289566</v>
+        <v>0.2496997714042664</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1709278374910355</v>
+        <v>0.2598388493061066</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1663774102926254</v>
+        <v>0.2649215757846832</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1600279957056046</v>
+        <v>0.2574713230133057</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1752427816390991</v>
+        <v>0.270641565322876</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2059743702411652</v>
+        <v>0.2937043011188507</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2060620039701462</v>
+        <v>0.2925337851047516</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.204648345708847</v>
+        <v>0.2909919917583466</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2112762182950974</v>
+        <v>0.2968530058860779</v>
       </c>
     </row>
     <row r="47">
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2347871065139771</v>
+        <v>0.3082880675792694</v>
       </c>
     </row>
     <row r="48">
@@ -956,10 +956,10 @@
         <v>0</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2617416977882385</v>
+        <v>0.3252207040786743</v>
       </c>
     </row>
     <row r="49">
@@ -967,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2781640589237213</v>
+        <v>0.3309074342250824</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3432162702083588</v>
+        <v>0.3479488790035248</v>
       </c>
     </row>
     <row r="51">
@@ -989,10 +989,10 @@
         <v>1</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2900806069374084</v>
+        <v>0.3233827948570251</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3090868890285492</v>
+        <v>0.3277689218521118</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3024193048477173</v>
+        <v>0.3276373744010925</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3328604698181152</v>
+        <v>0.3342135548591614</v>
       </c>
     </row>
     <row r="55">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2865410447120667</v>
+        <v>0.3031619787216187</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2838022112846375</v>
+        <v>0.2900123298168182</v>
       </c>
     </row>
     <row r="57">
@@ -1055,10 +1055,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2811754941940308</v>
+        <v>0.3026149570941925</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3058517277240753</v>
+        <v>0.3129000067710876</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.3377606272697449</v>
+        <v>0.3313346207141876</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2847247719764709</v>
+        <v>0.2981729209423065</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2690600156784058</v>
+        <v>0.293770968914032</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2388896495103836</v>
+        <v>0.2746015191078186</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2653325200080872</v>
+        <v>0.2845931053161621</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2902161478996277</v>
+        <v>0.2987082302570343</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2721323668956757</v>
+        <v>0.299798846244812</v>
       </c>
     </row>
     <row r="66">
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2728770077228546</v>
+        <v>0.3095797300338745</v>
       </c>
     </row>
     <row r="67">
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.2855453491210938</v>
+        <v>0.3127874135971069</v>
       </c>
     </row>
     <row r="68">
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2911399900913239</v>
+        <v>0.3111320436000824</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2712695002555847</v>
+        <v>0.2881104946136475</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2747787833213806</v>
+        <v>0.2853088676929474</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2665007710456848</v>
+        <v>0.2779954075813293</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1918675750494003</v>
+        <v>0.2919917106628418</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1737677901983261</v>
+        <v>0.2728104889392853</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1479853838682175</v>
+        <v>0.289881557226181</v>
       </c>
     </row>
     <row r="75">
@@ -1253,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1789795756340027</v>
+        <v>0.3000385165214539</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1836605817079544</v>
+        <v>0.2966263592243195</v>
       </c>
     </row>
     <row r="77">
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1925239711999893</v>
+        <v>0.3012711703777313</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1849002838134766</v>
+        <v>0.289389580488205</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1963022649288177</v>
+        <v>0.2870491147041321</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2002702206373215</v>
+        <v>0.2825881838798523</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1829532980918884</v>
+        <v>0.2780455052852631</v>
       </c>
     </row>
     <row r="82">
@@ -1330,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>0.2174079418182373</v>
+        <v>0.3147576153278351</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.2201119661331177</v>
+        <v>0.2908229529857635</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2117030024528503</v>
+        <v>0.2988648116588593</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1800681352615356</v>
+        <v>0.2763010561466217</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1816184669733047</v>
+        <v>0.274865448474884</v>
       </c>
     </row>
     <row r="87">
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>0.2291494756937027</v>
+        <v>0.306006908416748</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2050115913152695</v>
+        <v>0.2927651703357697</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2024649381637573</v>
+        <v>0.2948606014251709</v>
       </c>
     </row>
     <row r="90">
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2179196774959564</v>
+        <v>0.3077526390552521</v>
       </c>
     </row>
     <row r="91">
@@ -1429,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2412390112876892</v>
+        <v>0.3265544474124908</v>
       </c>
     </row>
     <row r="92">
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2399351000785828</v>
+        <v>0.3268657326698303</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1864273548126221</v>
+        <v>0.2630378603935242</v>
       </c>
     </row>
     <row r="94">
@@ -1462,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2245163917541504</v>
+        <v>0.3075506985187531</v>
       </c>
     </row>
     <row r="95">
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2291391640901566</v>
+        <v>0.3267741799354553</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1873904466629028</v>
+        <v>0.2662570178508759</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2067117542028427</v>
+        <v>0.2542386054992676</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3241853713989258</v>
+        <v>0.3390501737594604</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2102421075105667</v>
+        <v>0.2899646759033203</v>
       </c>
     </row>
     <row r="100">
@@ -1528,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2318217903375626</v>
+        <v>0.3000012636184692</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2403066158294678</v>
+        <v>0.2996857166290283</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2399089932441711</v>
+        <v>0.295087605714798</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2295450270175934</v>
+        <v>0.2896869480609894</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.2405727505683899</v>
+        <v>0.2927162349224091</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.24461829662323</v>
+        <v>0.2937803864479065</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0.2224791795015335</v>
+        <v>0.2852213978767395</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2433880269527435</v>
+        <v>0.2994324266910553</v>
       </c>
     </row>
     <row r="108">
@@ -1616,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108" t="n">
-        <v>0.24950310587883</v>
+        <v>0.3076993227005005</v>
       </c>
     </row>
     <row r="109">
@@ -1627,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2988097369670868</v>
+        <v>0.3363834619522095</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1433841437101364</v>
+        <v>0.2768828868865967</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1670248061418533</v>
+        <v>0.2923911511898041</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1804302483797073</v>
+        <v>0.2901846170425415</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1787750273942947</v>
+        <v>0.2920569777488708</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1716841161251068</v>
+        <v>0.2816106379032135</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1638062596321106</v>
+        <v>0.282250702381134</v>
       </c>
     </row>
     <row r="116">
@@ -1704,10 +1704,10 @@
         <v>0</v>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1949034333229065</v>
+        <v>0.3100714981555939</v>
       </c>
     </row>
     <row r="117">
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1934078484773636</v>
+        <v>0.3105649948120117</v>
       </c>
     </row>
     <row r="118">
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>0.2255610972642899</v>
+        <v>0.3286233246326447</v>
       </c>
     </row>
     <row r="119">
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2226466983556747</v>
+        <v>0.3316271007061005</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2166190147399902</v>
+        <v>0.2713590860366821</v>
       </c>
     </row>
     <row r="121">
@@ -1759,10 +1759,10 @@
         <v>1</v>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2742612957954407</v>
+        <v>0.3124756813049316</v>
       </c>
     </row>
     <row r="122">
@@ -1770,10 +1770,10 @@
         <v>1</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>0.255401223897934</v>
+        <v>0.3046939969062805</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0.2767384350299835</v>
+        <v>0.2959698140621185</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2475635558366776</v>
+        <v>0.2891551852226257</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0.250551164150238</v>
+        <v>0.297671765089035</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0.249022364616394</v>
+        <v>0.2902853786945343</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0.2319845259189606</v>
+        <v>0.2792885303497314</v>
       </c>
     </row>
     <row r="128">
@@ -1836,10 +1836,10 @@
         <v>1</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>0.263652503490448</v>
+        <v>0.3008041679859161</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2748886346817017</v>
+        <v>0.2998161315917969</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2624746263027191</v>
+        <v>0.2919549345970154</v>
       </c>
     </row>
     <row r="131">
@@ -1869,10 +1869,10 @@
         <v>1</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>0.2701574563980103</v>
+        <v>0.3018651604652405</v>
       </c>
     </row>
     <row r="132">
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>0.2955268323421478</v>
+        <v>0.3126275241374969</v>
       </c>
     </row>
     <row r="133">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2910527884960175</v>
+        <v>0.3333138227462769</v>
       </c>
     </row>
     <row r="134">
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>0.2334237694740295</v>
+        <v>0.3117635250091553</v>
       </c>
     </row>
     <row r="135">
@@ -1913,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>0.2364491820335388</v>
+        <v>0.3096433579921722</v>
       </c>
     </row>
     <row r="136">
@@ -1924,10 +1924,10 @@
         <v>0</v>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>0.2861479818820953</v>
+        <v>0.3255072832107544</v>
       </c>
     </row>
     <row r="137">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0.2746149599552155</v>
+        <v>0.3351421356201172</v>
       </c>
     </row>
     <row r="138">
@@ -1946,10 +1946,10 @@
         <v>0</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2777868509292603</v>
+        <v>0.3301644325256348</v>
       </c>
     </row>
     <row r="139">
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>0.2663631439208984</v>
+        <v>0.316480964422226</v>
       </c>
     </row>
     <row r="140">
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2583484351634979</v>
+        <v>0.3150219619274139</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0.2406353503465652</v>
+        <v>0.298509418964386</v>
       </c>
     </row>
     <row r="142">
@@ -1990,10 +1990,10 @@
         <v>1</v>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2551130652427673</v>
+        <v>0.3341828286647797</v>
       </c>
     </row>
     <row r="143">
@@ -2001,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>0.2794508635997772</v>
+        <v>0.3251211047172546</v>
       </c>
     </row>
     <row r="144">
@@ -2012,10 +2012,10 @@
         <v>1</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2909943163394928</v>
+        <v>0.3219552040100098</v>
       </c>
     </row>
     <row r="145">
@@ -2023,10 +2023,10 @@
         <v>1</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>0.2944423258304596</v>
+        <v>0.3099992275238037</v>
       </c>
     </row>
     <row r="146">
@@ -2034,10 +2034,10 @@
         <v>1</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0.2853884696960449</v>
+        <v>0.3114360868930817</v>
       </c>
     </row>
     <row r="147">
@@ -2045,10 +2045,10 @@
         <v>1</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>0.2816774845123291</v>
+        <v>0.3156703114509583</v>
       </c>
     </row>
     <row r="148">
@@ -2056,10 +2056,10 @@
         <v>1</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" t="n">
-        <v>0.2916271984577179</v>
+        <v>0.3240561187267303</v>
       </c>
     </row>
     <row r="149">
@@ -2067,10 +2067,10 @@
         <v>1</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C149" t="n">
-        <v>0.2839883863925934</v>
+        <v>0.3199943900108337</v>
       </c>
     </row>
     <row r="150">
@@ -2078,10 +2078,10 @@
         <v>1</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C150" t="n">
-        <v>0.2834880352020264</v>
+        <v>0.3248811960220337</v>
       </c>
     </row>
     <row r="151">
@@ -2089,10 +2089,10 @@
         <v>1</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>0.2799760699272156</v>
+        <v>0.3230020105838776</v>
       </c>
     </row>
     <row r="152">
@@ -2100,10 +2100,10 @@
         <v>1</v>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>0.2706081569194794</v>
+        <v>0.3184911906719208</v>
       </c>
     </row>
     <row r="153">
@@ -2111,10 +2111,10 @@
         <v>1</v>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>0.2615512013435364</v>
+        <v>0.3173831403255463</v>
       </c>
     </row>
     <row r="154">
@@ -2122,10 +2122,10 @@
         <v>1</v>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C154" t="n">
-        <v>0.2731585502624512</v>
+        <v>0.33001908659935</v>
       </c>
     </row>
   </sheetData>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -450,10 +450,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3352309465408325</v>
+        <v>0.2754518687725067</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3035429418087006</v>
+        <v>0.2302015274763107</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.294698178768158</v>
+        <v>0.2194328308105469</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3082067370414734</v>
+        <v>0.2428061068058014</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +494,10 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3024156391620636</v>
+        <v>0.2314937561750412</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3188870251178741</v>
+        <v>0.2612113654613495</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2729175388813019</v>
+        <v>0.1724368333816528</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +527,10 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3027096390724182</v>
+        <v>0.2069623470306396</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3008955419063568</v>
+        <v>0.195002406835556</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3119738101959229</v>
+        <v>0.2228653728961945</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3028473854064941</v>
+        <v>0.2116249948740005</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2963594794273376</v>
+        <v>0.2018693387508392</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2799627482891083</v>
+        <v>0.1807868182659149</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +593,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3011156320571899</v>
+        <v>0.2150056213140488</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +604,10 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3097865581512451</v>
+        <v>0.2234154343605042</v>
       </c>
     </row>
     <row r="17">
@@ -615,10 +615,10 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3424755930900574</v>
+        <v>0.2883488833904266</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3291063606739044</v>
+        <v>0.2636538743972778</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +637,10 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3277017176151276</v>
+        <v>0.2535077035427094</v>
       </c>
     </row>
     <row r="20">
@@ -648,10 +648,10 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3446286618709564</v>
+        <v>0.2896242737770081</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +659,10 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3140000402927399</v>
+        <v>0.2392026633024216</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3034732341766357</v>
+        <v>0.2249775826931</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3103814721107483</v>
+        <v>0.233772337436676</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +692,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3156424462795258</v>
+        <v>0.2418071776628494</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +703,10 @@
         <v>0</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3098143637180328</v>
+        <v>0.238581970334053</v>
       </c>
     </row>
     <row r="26">
@@ -714,10 +714,10 @@
         <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3161989748477936</v>
+        <v>0.2482118159532547</v>
       </c>
     </row>
     <row r="27">
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3218830227851868</v>
+        <v>0.2545632421970367</v>
       </c>
     </row>
     <row r="28">
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3440283238887787</v>
+        <v>0.2939884960651398</v>
       </c>
     </row>
     <row r="29">
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3393272459506989</v>
+        <v>0.2844802737236023</v>
       </c>
     </row>
     <row r="30">
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3318997919559479</v>
+        <v>0.2554483115673065</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2955625951290131</v>
+        <v>0.2147109657526016</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2794621586799622</v>
+        <v>0.1918294578790665</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2908841073513031</v>
+        <v>0.2126893401145935</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2892663776874542</v>
+        <v>0.209849089384079</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2934877574443817</v>
+        <v>0.2154132276773453</v>
       </c>
     </row>
     <row r="36">
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3180401623249054</v>
+        <v>0.2667926847934723</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2548227906227112</v>
+        <v>0.1509274393320084</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2496997714042664</v>
+        <v>0.1423744410276413</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2598388493061066</v>
+        <v>0.1511752754449844</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2649215757846832</v>
+        <v>0.1700384467840195</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2574713230133057</v>
+        <v>0.1605497896671295</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.270641565322876</v>
+        <v>0.1761105507612228</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2937043011188507</v>
+        <v>0.2129127681255341</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2925337851047516</v>
+        <v>0.213084802031517</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2909919917583466</v>
+        <v>0.2103063017129898</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2968530058860779</v>
+        <v>0.2165477573871613</v>
       </c>
     </row>
     <row r="47">
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3082880675792694</v>
+        <v>0.2367149889469147</v>
       </c>
     </row>
     <row r="48">
@@ -956,10 +956,10 @@
         <v>0</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3252207040786743</v>
+        <v>0.270606130361557</v>
       </c>
     </row>
     <row r="49">
@@ -967,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3309074342250824</v>
+        <v>0.2805975079536438</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3479488790035248</v>
+        <v>0.3006947636604309</v>
       </c>
     </row>
     <row r="51">
@@ -989,10 +989,10 @@
         <v>1</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3233827948570251</v>
+        <v>0.2474376708269119</v>
       </c>
     </row>
     <row r="52">
@@ -1000,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3277689218521118</v>
+        <v>0.2609423696994781</v>
       </c>
     </row>
     <row r="53">
@@ -1011,10 +1011,10 @@
         <v>1</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3276373744010925</v>
+        <v>0.2599968314170837</v>
       </c>
     </row>
     <row r="54">
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3342135548591614</v>
+        <v>0.2769288420677185</v>
       </c>
     </row>
     <row r="55">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3031619787216187</v>
+        <v>0.2163293808698654</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2900123298168182</v>
+        <v>0.2053877264261246</v>
       </c>
     </row>
     <row r="57">
@@ -1055,10 +1055,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3026149570941925</v>
+        <v>0.2091684192419052</v>
       </c>
     </row>
     <row r="58">
@@ -1066,10 +1066,10 @@
         <v>1</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3129000067710876</v>
+        <v>0.2314578890800476</v>
       </c>
     </row>
     <row r="59">
@@ -1077,10 +1077,10 @@
         <v>1</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0.3313346207141876</v>
+        <v>0.276826024055481</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2981729209423065</v>
+        <v>0.200527623295784</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0.293770968914032</v>
+        <v>0.2101186066865921</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2746015191078186</v>
+        <v>0.1839614510536194</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2845931053161621</v>
+        <v>0.2082868367433548</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2987082302570343</v>
+        <v>0.230978935956955</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.299798846244812</v>
+        <v>0.2280938625335693</v>
       </c>
     </row>
     <row r="66">
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3095797300338745</v>
+        <v>0.2435422986745834</v>
       </c>
     </row>
     <row r="67">
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3127874135971069</v>
+        <v>0.24562107026577</v>
       </c>
     </row>
     <row r="68">
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3111320436000824</v>
+        <v>0.2441948801279068</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2881104946136475</v>
+        <v>0.2103318125009537</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2853088676929474</v>
+        <v>0.2069510221481323</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2779954075813293</v>
+        <v>0.1955811679363251</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2919917106628418</v>
+        <v>0.205917552113533</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2728104889392853</v>
+        <v>0.1701053828001022</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.289881557226181</v>
+        <v>0.2080631852149963</v>
       </c>
     </row>
     <row r="75">
@@ -1253,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3000385165214539</v>
+        <v>0.2092165499925613</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2966263592243195</v>
+        <v>0.2115912586450577</v>
       </c>
     </row>
     <row r="77">
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3012711703777313</v>
+        <v>0.2149430960416794</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.289389580488205</v>
+        <v>0.191960945725441</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2870491147041321</v>
+        <v>0.2003437578678131</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2825881838798523</v>
+        <v>0.1990787386894226</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2780455052852631</v>
+        <v>0.1903322041034698</v>
       </c>
     </row>
     <row r="82">
@@ -1330,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3147576153278351</v>
+        <v>0.2567127645015717</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.2908229529857635</v>
+        <v>0.2053187638521194</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2988648116588593</v>
+        <v>0.2202191650867462</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2763010561466217</v>
+        <v>0.1839149594306946</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.274865448474884</v>
+        <v>0.1796631813049316</v>
       </c>
     </row>
     <row r="87">
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0.306006908416748</v>
+        <v>0.2355704754590988</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2927651703357697</v>
+        <v>0.2118220627307892</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2948606014251709</v>
+        <v>0.2192685157060623</v>
       </c>
     </row>
     <row r="90">
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3077526390552521</v>
+        <v>0.2439772635698318</v>
       </c>
     </row>
     <row r="91">
@@ -1429,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3265544474124908</v>
+        <v>0.269464373588562</v>
       </c>
     </row>
     <row r="92">
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3268657326698303</v>
+        <v>0.263929009437561</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2630378603935242</v>
+        <v>0.1612281054258347</v>
       </c>
     </row>
     <row r="94">
@@ -1462,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3075506985187531</v>
+        <v>0.2327719032764435</v>
       </c>
     </row>
     <row r="95">
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3267741799354553</v>
+        <v>0.2617701590061188</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2662570178508759</v>
+        <v>0.1664444506168365</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2542386054992676</v>
+        <v>0.122186079621315</v>
       </c>
     </row>
     <row r="98">
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3390501737594604</v>
+        <v>0.2624230980873108</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2899646759033203</v>
+        <v>0.1993002891540527</v>
       </c>
     </row>
     <row r="100">
@@ -1528,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3000012636184692</v>
+        <v>0.2156563401222229</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2996857166290283</v>
+        <v>0.2162761986255646</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.295087605714798</v>
+        <v>0.2084864675998688</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2896869480609894</v>
+        <v>0.2007590532302856</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.2927162349224091</v>
+        <v>0.2085608839988708</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2937803864479065</v>
+        <v>0.2099000662565231</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0.2852213978767395</v>
+        <v>0.1934780180454254</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2994324266910553</v>
+        <v>0.2153976410627365</v>
       </c>
     </row>
     <row r="108">
@@ -1616,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0.3076993227005005</v>
+        <v>0.2270591408014297</v>
       </c>
     </row>
     <row r="109">
@@ -1627,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3363834619522095</v>
+        <v>0.2713084816932678</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0.2768828868865967</v>
+        <v>0.1797033399343491</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0.2923911511898041</v>
+        <v>0.2189555168151855</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0.2901846170425415</v>
+        <v>0.2212684899568558</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2920569777488708</v>
+        <v>0.2207718044519424</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.2816106379032135</v>
+        <v>0.2029401659965515</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0.282250702381134</v>
+        <v>0.2047753483057022</v>
       </c>
     </row>
     <row r="116">
@@ -1704,10 +1704,10 @@
         <v>0</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>0.3100714981555939</v>
+        <v>0.2419986426830292</v>
       </c>
     </row>
     <row r="117">
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>0.3105649948120117</v>
+        <v>0.2535172700881958</v>
       </c>
     </row>
     <row r="118">
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0.3286233246326447</v>
+        <v>0.2815767228603363</v>
       </c>
     </row>
     <row r="119">
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>0.3316271007061005</v>
+        <v>0.2821485102176666</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2713590860366821</v>
+        <v>0.1679172515869141</v>
       </c>
     </row>
     <row r="121">
@@ -1759,10 +1759,10 @@
         <v>1</v>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0.3124756813049316</v>
+        <v>0.2435875087976456</v>
       </c>
     </row>
     <row r="122">
@@ -1770,10 +1770,10 @@
         <v>1</v>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0.3046939969062805</v>
+        <v>0.2506540715694427</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0.2959698140621185</v>
+        <v>0.2417242825031281</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2891551852226257</v>
+        <v>0.2284255176782608</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0.297671765089035</v>
+        <v>0.2379655987024307</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0.2902853786945343</v>
+        <v>0.2275890111923218</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0.2792885303497314</v>
+        <v>0.2080255895853043</v>
       </c>
     </row>
     <row r="128">
@@ -1836,10 +1836,10 @@
         <v>1</v>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.3008041679859161</v>
+        <v>0.2450581192970276</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2998161315917969</v>
+        <v>0.2467469573020935</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2919549345970154</v>
+        <v>0.2328972369432449</v>
       </c>
     </row>
     <row r="131">
@@ -1869,10 +1869,10 @@
         <v>1</v>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3018651604652405</v>
+        <v>0.2444811016321182</v>
       </c>
     </row>
     <row r="132">
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>0.3126275241374969</v>
+        <v>0.2620181739330292</v>
       </c>
     </row>
     <row r="133">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>0.3333138227462769</v>
+        <v>0.2869152128696442</v>
       </c>
     </row>
     <row r="134">
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>0.3117635250091553</v>
+        <v>0.2515680193901062</v>
       </c>
     </row>
     <row r="135">
@@ -1913,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>0.3096433579921722</v>
+        <v>0.2546007633209229</v>
       </c>
     </row>
     <row r="136">
@@ -1924,10 +1924,10 @@
         <v>0</v>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0.3255072832107544</v>
+        <v>0.2766465544700623</v>
       </c>
     </row>
     <row r="137">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>0.3351421356201172</v>
+        <v>0.2850992381572723</v>
       </c>
     </row>
     <row r="138">
@@ -1946,10 +1946,10 @@
         <v>0</v>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>0.3301644325256348</v>
+        <v>0.2776720523834229</v>
       </c>
     </row>
     <row r="139">
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>0.316480964422226</v>
+        <v>0.2560079097747803</v>
       </c>
     </row>
     <row r="140">
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>0.3150219619274139</v>
+        <v>0.2548176944255829</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0.298509418964386</v>
+        <v>0.2012928575277328</v>
       </c>
     </row>
     <row r="142">
@@ -1990,10 +1990,10 @@
         <v>1</v>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>0.3341828286647797</v>
+        <v>0.2991587519645691</v>
       </c>
     </row>
     <row r="143">
@@ -2001,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0.3251211047172546</v>
+        <v>0.2914817929267883</v>
       </c>
     </row>
     <row r="144">
@@ -2012,10 +2012,10 @@
         <v>1</v>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>0.3219552040100098</v>
+        <v>0.28823122382164</v>
       </c>
     </row>
     <row r="145">
@@ -2023,10 +2023,10 @@
         <v>1</v>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3099992275238037</v>
+        <v>0.2722382843494415</v>
       </c>
     </row>
     <row r="146">
@@ -2034,10 +2034,10 @@
         <v>1</v>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>0.3114360868930817</v>
+        <v>0.269269734621048</v>
       </c>
     </row>
     <row r="147">
@@ -2045,10 +2045,10 @@
         <v>1</v>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>0.3156703114509583</v>
+        <v>0.2718342542648315</v>
       </c>
     </row>
     <row r="148">
@@ -2056,10 +2056,10 @@
         <v>1</v>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0.3240561187267303</v>
+        <v>0.2855881750583649</v>
       </c>
     </row>
     <row r="149">
@@ -2067,10 +2067,10 @@
         <v>1</v>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0.3199943900108337</v>
+        <v>0.2782599925994873</v>
       </c>
     </row>
     <row r="150">
@@ -2078,10 +2078,10 @@
         <v>1</v>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0.3248811960220337</v>
+        <v>0.2866683006286621</v>
       </c>
     </row>
     <row r="151">
@@ -2089,10 +2089,10 @@
         <v>1</v>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>0.3230020105838776</v>
+        <v>0.2837556004524231</v>
       </c>
     </row>
     <row r="152">
@@ -2100,10 +2100,10 @@
         <v>1</v>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>0.3184911906719208</v>
+        <v>0.2740334570407867</v>
       </c>
     </row>
     <row r="153">
@@ -2111,10 +2111,10 @@
         <v>1</v>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0.3173831403255463</v>
+        <v>0.2720801532268524</v>
       </c>
     </row>
     <row r="154">
@@ -2122,10 +2122,10 @@
         <v>1</v>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>0.33001908659935</v>
+        <v>0.2958225011825562</v>
       </c>
     </row>
   </sheetData>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,101 +447,101 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2754518687725067</v>
+        <v>0.3998164534568787</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2302015274763107</v>
+        <v>0.3746602237224579</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2194328308105469</v>
+        <v>0.3626834154129028</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2428061068058014</v>
+        <v>0.3609279692173004</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2314937561750412</v>
+        <v>0.389222264289856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2612113654613495</v>
+        <v>0.2552606463432312</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1724368333816528</v>
+        <v>0.3058193624019623</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2069623470306396</v>
+        <v>0.3074795603752136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.195002406835556</v>
+        <v>0.4013607501983643</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2228653728961945</v>
+        <v>0.2613039910793304</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2116249948740005</v>
+        <v>0.2225780338048935</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2018693387508392</v>
+        <v>0.2176714390516281</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1807868182659149</v>
+        <v>0.2253583371639252</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2150056213140488</v>
+        <v>0.2573859393596649</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2234154343605042</v>
+        <v>0.2528567314147949</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2883488833904266</v>
+        <v>0.2873608767986298</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636538743972778</v>
+        <v>0.3212756216526031</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2535077035427094</v>
+        <v>0.2670582830905914</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2896242737770081</v>
+        <v>0.1316131055355072</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2392026633024216</v>
+        <v>0.1554965227842331</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2249775826931</v>
+        <v>0.1151797696948051</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.233772337436676</v>
+        <v>0.05716857314109802</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +692,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2418071776628494</v>
+        <v>0.3209474384784698</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.238581970334053</v>
+        <v>0.2443314492702484</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2482118159532547</v>
+        <v>0.1937031745910645</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2545632421970367</v>
+        <v>0.1815987676382065</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2939884960651398</v>
+        <v>0.1829021126031876</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2844802737236023</v>
+        <v>0.2721526622772217</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2554483115673065</v>
+        <v>0.2924136221408844</v>
       </c>
     </row>
     <row r="31">
@@ -769,10 +769,10 @@
         <v>0</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2147109657526016</v>
+        <v>0.3035025894641876</v>
       </c>
     </row>
     <row r="32">
@@ -780,197 +780,197 @@
         <v>0</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1918294578790665</v>
+        <v>0.3205216228961945</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2126893401145935</v>
+        <v>0.3616923689842224</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.209849089384079</v>
+        <v>0.2721300423145294</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2154132276773453</v>
+        <v>0.2614982724189758</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2667926847934723</v>
+        <v>0.3000155091285706</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1509274393320084</v>
+        <v>0.2789759039878845</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1423744410276413</v>
+        <v>0.288376659154892</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1511752754449844</v>
+        <v>0.3531848192214966</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1700384467840195</v>
+        <v>0.3542061448097229</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1605497896671295</v>
+        <v>0.3898757994174957</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1761105507612228</v>
+        <v>0.3702403008937836</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2129127681255341</v>
+        <v>0.2579503059387207</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.213084802031517</v>
+        <v>0.1649575978517532</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2103063017129898</v>
+        <v>0.2088363766670227</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2165477573871613</v>
+        <v>0.19410739839077</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2367149889469147</v>
+        <v>0.2264760285615921</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.270606130361557</v>
+        <v>0.2465545982122421</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2805975079536438</v>
+        <v>0.1693480163812637</v>
       </c>
     </row>
     <row r="50">
@@ -978,10 +978,10 @@
         <v>1</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3006947636604309</v>
+        <v>0.1629230231046677</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2474376708269119</v>
+        <v>0.1802303493022919</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2609423696994781</v>
+        <v>0.1734326034784317</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2599968314170837</v>
+        <v>0.1108786538243294</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2769288420677185</v>
+        <v>0.134749099612236</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2163293808698654</v>
+        <v>0.2065716683864594</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2053877264261246</v>
+        <v>0.2288726419210434</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2091684192419052</v>
+        <v>0.2026878893375397</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2314578890800476</v>
+        <v>0.2096738964319229</v>
       </c>
     </row>
     <row r="59">
@@ -1080,29 +1080,29 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0.276826024055481</v>
+        <v>0.2248986512422562</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>0.200527623295784</v>
+        <v>0.3078555762767792</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2101186066865921</v>
+        <v>0.3442550897598267</v>
       </c>
     </row>
     <row r="62">
@@ -1110,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1839614510536194</v>
+        <v>0.3800090849399567</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2082868367433548</v>
+        <v>0.2876547873020172</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.230978935956955</v>
+        <v>0.282151073217392</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2280938625335693</v>
+        <v>0.2698885798454285</v>
       </c>
     </row>
     <row r="66">
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2435422986745834</v>
+        <v>0.3204776644706726</v>
       </c>
     </row>
     <row r="67">
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.24562107026577</v>
+        <v>0.3252553939819336</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2441948801279068</v>
+        <v>0.2730304002761841</v>
       </c>
     </row>
     <row r="69">
@@ -1187,10 +1187,10 @@
         <v>0</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2103318125009537</v>
+        <v>0.30720454454422</v>
       </c>
     </row>
     <row r="70">
@@ -1198,10 +1198,10 @@
         <v>0</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2069510221481323</v>
+        <v>0.306972473859787</v>
       </c>
     </row>
     <row r="71">
@@ -1209,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1955811679363251</v>
+        <v>0.3574160039424896</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.205917552113533</v>
+        <v>0.2145256847143173</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1701053828001022</v>
+        <v>0.1079578027129173</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2080631852149963</v>
+        <v>0.2928792238235474</v>
       </c>
     </row>
     <row r="75">
@@ -1253,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2092165499925613</v>
+        <v>0.3170457780361176</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2115912586450577</v>
+        <v>0.294952392578125</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.2149430960416794</v>
+        <v>0.2613224387168884</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.191960945725441</v>
+        <v>0.2205575853586197</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2003437578678131</v>
+        <v>0.2349432110786438</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1990787386894226</v>
+        <v>0.1762616634368896</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1903322041034698</v>
+        <v>0.1661624610424042</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.2567127645015717</v>
+        <v>0.2750129103660583</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.2053187638521194</v>
+        <v>0.140312522649765</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2202191650867462</v>
+        <v>0.2637098729610443</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1839149594306946</v>
+        <v>0.1899506598711014</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1796631813049316</v>
+        <v>0.1938899457454681</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0.2355704754590988</v>
+        <v>0.2758829593658447</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2118220627307892</v>
+        <v>0.2160639762878418</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2192685157060623</v>
+        <v>0.2266378849744797</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2439772635698318</v>
+        <v>0.2506541311740875</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.269464373588562</v>
+        <v>0.2796632945537567</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.263929009437561</v>
+        <v>0.2616449296474457</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1612281054258347</v>
+        <v>0.1141601726412773</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2327719032764435</v>
+        <v>0.2303149104118347</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2617701590061188</v>
+        <v>0.2642280459403992</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1664444506168365</v>
+        <v>0.1430838704109192</v>
       </c>
     </row>
     <row r="97">
@@ -1495,10 +1495,10 @@
         <v>0</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0.122186079621315</v>
+        <v>0.3077728152275085</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2624230980873108</v>
+        <v>0.2597647607326508</v>
       </c>
     </row>
     <row r="99">
@@ -1517,10 +1517,10 @@
         <v>0</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1993002891540527</v>
+        <v>0.3819040358066559</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2156563401222229</v>
+        <v>0.2406705915927887</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2162761986255646</v>
+        <v>0.2433031499385834</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2084864675998688</v>
+        <v>0.2192561477422714</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2007590532302856</v>
+        <v>0.2157271653413773</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.2085608839988708</v>
+        <v>0.1973535865545273</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2099000662565231</v>
+        <v>0.2351019829511642</v>
       </c>
     </row>
     <row r="106">
@@ -1594,10 +1594,10 @@
         <v>0</v>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1934780180454254</v>
+        <v>0.3153581917285919</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2153976410627365</v>
+        <v>0.1105381101369858</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2270591408014297</v>
+        <v>0.06978912651538849</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2713084816932678</v>
+        <v>0.05104561522603035</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1797033399343491</v>
+        <v>0.04392140358686447</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0.2189555168151855</v>
+        <v>0.09835971891880035</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0.2212684899568558</v>
+        <v>0.2821978330612183</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2207718044519424</v>
+        <v>0.06187628209590912</v>
       </c>
     </row>
     <row r="114">
@@ -1682,10 +1682,10 @@
         <v>0</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>0.2029401659965515</v>
+        <v>0.3899979591369629</v>
       </c>
     </row>
     <row r="115">
@@ -1693,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2047753483057022</v>
+        <v>0.3264510631561279</v>
       </c>
     </row>
     <row r="116">
@@ -1704,10 +1704,10 @@
         <v>0</v>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>0.2419986426830292</v>
+        <v>0.3108426928520203</v>
       </c>
     </row>
     <row r="117">
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>0.2535172700881958</v>
+        <v>0.3000702857971191</v>
       </c>
     </row>
     <row r="118">
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>0.2815767228603363</v>
+        <v>0.3198405504226685</v>
       </c>
     </row>
     <row r="119">
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2821485102176666</v>
+        <v>0.3335399627685547</v>
       </c>
     </row>
     <row r="120">
@@ -1748,153 +1748,153 @@
         <v>0</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1679172515869141</v>
+        <v>0.3498071134090424</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2435875087976456</v>
+        <v>0.1627717614173889</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0.2506540715694427</v>
+        <v>0.1871021091938019</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0.2417242825031281</v>
+        <v>0.2849530875682831</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2284255176782608</v>
+        <v>0.06395889818668365</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0.2379655987024307</v>
+        <v>0.05003310367465019</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0.2275890111923218</v>
+        <v>0.02468083798885345</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0.2080255895853043</v>
+        <v>0.03154606372117996</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2450581192970276</v>
+        <v>0.07102826982736588</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2467469573020935</v>
+        <v>0.1298578977584839</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2328972369432449</v>
+        <v>0.2368694990873337</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0.2444811016321182</v>
+        <v>0.05478541553020477</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>0.2620181739330292</v>
+        <v>0.038228839635849</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2869152128696442</v>
+        <v>0.06185803562402725</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>0.2515680193901062</v>
+        <v>0.01971000991761684</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>0.2546007633209229</v>
+        <v>0.03376632556319237</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0.2766465544700623</v>
+        <v>0.03034376166760921</v>
       </c>
     </row>
     <row r="137">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0.2850992381572723</v>
+        <v>0.3062372803688049</v>
       </c>
     </row>
     <row r="138">
@@ -1946,10 +1946,10 @@
         <v>0</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2776720523834229</v>
+        <v>0.3097639381885529</v>
       </c>
     </row>
     <row r="139">
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>0.2560079097747803</v>
+        <v>0.3169723153114319</v>
       </c>
     </row>
     <row r="140">
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2548176944255829</v>
+        <v>0.3217049241065979</v>
       </c>
     </row>
     <row r="141">
@@ -1979,153 +1979,98 @@
         <v>0</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>0.2012928575277328</v>
+        <v>0.3271548449993134</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2991587519645691</v>
+        <v>0.340770423412323</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>0.2914817929267883</v>
+        <v>0.322647750377655</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.28823122382164</v>
+        <v>0.3166584670543671</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B145" t="n">
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>0.2722382843494415</v>
+        <v>0.2330660969018936</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B146" t="n">
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>0.269269734621048</v>
+        <v>0.1893436014652252</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B147" t="n">
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>0.2718342542648315</v>
+        <v>0.1256543546915054</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B148" t="n">
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0.2855881750583649</v>
+        <v>0.1119693294167519</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B149" t="n">
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0.2782599925994873</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>1</v>
-      </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
-      <c r="C150" t="n">
-        <v>0.2866683006286621</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>1</v>
-      </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0.2837556004524231</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>1</v>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0.2740334570407867</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>1</v>
-      </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" t="n">
-        <v>0.2720801532268524</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>1</v>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" t="n">
-        <v>0.2958225011825562</v>
+        <v>0.1039045378565788</v>
       </c>
     </row>
   </sheetData>
